--- a/03_Features/04_Proteins/c_data/02_confirmation.xlsx
+++ b/03_Features/04_Proteins/c_data/02_confirmation.xlsx
@@ -7,12 +7,13 @@
   </bookViews>
   <sheets>
     <sheet name="confirmation" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="sweep_calibration" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t xml:space="preserve">label</t>
   </si>
@@ -38,16 +39,49 @@
     <t xml:space="preserve">p_count</t>
   </si>
   <si>
+    <t xml:space="preserve">given</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Training_Interaction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acute_Interaction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fcsa_I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nfibre_mixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nfibre_I</t>
+  </si>
+  <si>
     <t xml:space="preserve">mcsa</t>
   </si>
   <si>
-    <t xml:space="preserve">Baseline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Training_Interaction</t>
+    <t xml:space="preserve">1rm_legpress</t>
   </si>
   <si>
     <t xml:space="preserve">1rm_ext</t>
+  </si>
+  <si>
+    <t xml:space="preserve">volume_load</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">observed_hit_cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">expected_hit_cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p_binomial</t>
   </si>
 </sst>
 </file>
@@ -410,22 +444,22 @@
         <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00000997065530148305</v>
+        <v>0.00098048316612836</v>
       </c>
       <c r="E2" t="n">
-        <v>0.157157157157157</v>
+        <v>0.177177177177177</v>
       </c>
       <c r="F2" t="n">
-        <v>0.620620620620621</v>
+        <v>0.595595595595596</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00000655752744435272</v>
+        <v>0.00000599397538364371</v>
       </c>
       <c r="H2" t="n">
-        <v>0.056</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -439,16 +473,16 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0000480844883126368</v>
+        <v>0.00049988650376383</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0880880880880881</v>
+        <v>0.0940940940940941</v>
       </c>
       <c r="F3" t="n">
-        <v>0.241241241241241</v>
+        <v>0.257257257257257</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0000177233932279533</v>
+        <v>0.0000156468982612075</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -456,54 +490,613 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0000160429529091638</v>
+        <v>0.00042248044776145</v>
       </c>
       <c r="E4" t="n">
-        <v>0.129129129129129</v>
+        <v>0.0630630630630631</v>
       </c>
       <c r="F4" t="n">
-        <v>0.295295295295295</v>
+        <v>0.0780780780780781</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0000101802684581865</v>
+        <v>0.0000234808379513843</v>
       </c>
       <c r="H4" t="n">
-        <v>0.13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.000302853674124607</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.184184184184184</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.519519519519519</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.00000524113431220205</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.00548206579316934</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.105105105105105</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.402402402402402</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.000013491517209034</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
         <v>11</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.000401831099088446</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0620620620620621</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0750750750750751</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.0000237963021344958</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.000593947686113609</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.157157157157157</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.545545545545546</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.00000507615936980163</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
         <v>10</v>
       </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.000775478467062551</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0950950950950951</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.292292292292292</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0000116348717651507</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.0000279649178454927</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.0540540540540541</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.0800800800800801</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.000024713192666327</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.000264333229856517</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.178178178178178</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.677677677677678</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.00000550246193658144</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.00074528948820503</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.0670670670670671</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.164164164164164</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0000218856748035685</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.000207256250525036</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.043043043043043</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.0580580580580581</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.0000314059488495813</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.00000997065530148305</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.174174174174174</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.557557557557558</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.00000581661874025808</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.054</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.0000480844883126368</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.0890890890890891</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.227227227227227</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0000145414631880879</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.000968514548208467</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.0600600600600601</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.0710710710710711</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.0000209471609143459</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.000105827736812797</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.171171171171171</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.588588588588589</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.00000543144481897615</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.0000443735335865146</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.0800800800800801</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.193193193193193</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.0000185784609264742</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.00218291321984828</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.0540540540540541</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.0720720720720721</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.0000285889412809738</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.0000160429529091638</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.145145145145145</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.517517517517518</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.00000886394275114027</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.146</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
         <v>0.000109563975465294</v>
       </c>
-      <c r="E5" t="n">
-        <v>0.0810810810810811</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.123123123123123</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.0000186799376472242</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
+      <c r="E21" t="n">
+        <v>0.0970970970970971</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.183183183183183</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.00000789173047320952</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.000149344976960053</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.0880880880880881</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.119119119119119</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.0000134135115256155</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.000128175769067842</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.178178178178178</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.746746746746747</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.00000495763323784646</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.00225753919588513</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.0980980980980981</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.349349349349349</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.0000126038326998451</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.0000607597770027031</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.0610610610610611</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.0790790790790791</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.000022612669794723</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.57657657657658</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.74542413462819</v>
       </c>
     </row>
   </sheetData>
